--- a/codespace/DetroitRiverCase/results/ch4_fw2_c2_bray_curtis_dissimilarity_matrix.xlsx
+++ b/codespace/DetroitRiverCase/results/ch4_fw2_c2_bray_curtis_dissimilarity_matrix.xlsx
@@ -1340,10 +1340,10 @@
         <v>0.6441698352344741</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.2810952692828789</v>
+        <v>0.08815737600805186</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.564058747732799</v>
+        <v>0.5905151222264058</v>
       </c>
     </row>
     <row r="3">
@@ -1686,10 +1686,10 @@
         <v>0.9406683219532381</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.9199561201605272</v>
+        <v>0.9328578615307622</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.9040777537289109</v>
+        <v>0.926555888234502</v>
       </c>
     </row>
     <row r="4">
@@ -2032,10 +2032,10 @@
         <v>0.750805152979066</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.63353608863377</v>
+        <v>0.4789075200208932</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.680204066728038</v>
+        <v>0.7233781923675132</v>
       </c>
     </row>
     <row r="5">
@@ -2378,10 +2378,10 @@
         <v>0.7068764568764568</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.5310608484754228</v>
+        <v>0.3905256701093761</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.6370768914184206</v>
+        <v>0.6547923607682997</v>
       </c>
     </row>
     <row r="6">
@@ -2724,10 +2724,10 @@
         <v>0.5242616033755273</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.2797910340899978</v>
+        <v>0.1258144391887106</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.4368289056824829</v>
+        <v>0.4751240987034192</v>
       </c>
     </row>
     <row r="7">
@@ -3070,10 +3070,10 @@
         <v>0.7056574923547398</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.4581229828265522</v>
+        <v>0.3393606001936521</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.6335075760677472</v>
+        <v>0.6533221289353753</v>
       </c>
     </row>
     <row r="8">
@@ -3416,10 +3416,10 @@
         <v>0.5037037037037039</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.6067343942784607</v>
+        <v>0.3854181526823103</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.3881858254524245</v>
+        <v>0.4691311286591971</v>
       </c>
     </row>
     <row r="9">
@@ -3762,10 +3762,10 @@
         <v>0.5977477477477476</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.5292392949469377</v>
+        <v>0.3359133790330499</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.5261934131398841</v>
+        <v>0.5546572487259466</v>
       </c>
     </row>
     <row r="10">
@@ -4108,10 +4108,10 @@
         <v>0.1889978213507623</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.6299933119085522</v>
+        <v>0.5404155559736292</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.2237960570356418</v>
+        <v>0.1455691952602586</v>
       </c>
     </row>
     <row r="11">
@@ -4454,10 +4454,10 @@
         <v>0.3257967269595175</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.6089326963550769</v>
+        <v>0.399144051566048</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.2383760068130767</v>
+        <v>0.2985445069254152</v>
       </c>
     </row>
     <row r="12">
@@ -4800,10 +4800,10 @@
         <v>0.07870370370370347</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.7810668821859362</v>
+        <v>0.6682940585465554</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.2555563553357998</v>
+        <v>0.1008652528364949</v>
       </c>
     </row>
     <row r="13">
@@ -5146,10 +5146,10 @@
         <v>0.6442643388515905</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.6012785015129102</v>
+        <v>0.3897405983996379</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.5452722820842487</v>
+        <v>0.6087085679272927</v>
       </c>
     </row>
     <row r="14">
@@ -5492,10 +5492,10 @@
         <v>0.9194571283612379</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.7207853862894091</v>
+        <v>0.6465534591857616</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.8582181626984178</v>
+        <v>0.8827853033521215</v>
       </c>
     </row>
     <row r="15">
@@ -5838,10 +5838,10 @@
         <v>0.861111111111111</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.5091730472609882</v>
+        <v>0.5072332325003721</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.8284911454513667</v>
+        <v>0.827710021973958</v>
       </c>
     </row>
     <row r="16">
@@ -6184,10 +6184,10 @@
         <v>0.9166666666666667</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.6870971842911479</v>
+        <v>0.6198244247721296</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.8760221246783719</v>
+        <v>0.8643313032473021</v>
       </c>
     </row>
     <row r="17">
@@ -6530,10 +6530,10 @@
         <v>0.4572072072072069</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.4679244910802386</v>
+        <v>0.2826069357075954</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.355772345172752</v>
+        <v>0.4086222026909004</v>
       </c>
     </row>
     <row r="18">
@@ -6876,10 +6876,10 @@
         <v>0.3642857142857141</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.5835532910326737</v>
+        <v>0.4632787697001843</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.2129670815997454</v>
+        <v>0.3139155682909374</v>
       </c>
     </row>
     <row r="19">
@@ -7222,10 +7222,10 @@
         <v>0.8072916666666667</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.5791640224008996</v>
+        <v>0.5245112663737305</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.748652555242988</v>
+        <v>0.7592124726805903</v>
       </c>
     </row>
     <row r="20">
@@ -7568,10 +7568,10 @@
         <v>0.07984607984607978</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.697810125671108</v>
+        <v>0.6025332098101377</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.2419884893811775</v>
+        <v>0.07810538939197756</v>
       </c>
     </row>
     <row r="21">
@@ -7914,10 +7914,10 @@
         <v>0.03717948717948739</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.8047408477543434</v>
+        <v>0.6872555297437253</v>
       </c>
       <c r="DJ21" t="n">
-        <v>0.2979024161386215</v>
+        <v>0.1375859546086068</v>
       </c>
     </row>
     <row r="22">
@@ -8260,10 +8260,10 @@
         <v>0.0696347031963471</v>
       </c>
       <c r="DI22" t="n">
-        <v>0.8403877870396534</v>
+        <v>0.7197107457605849</v>
       </c>
       <c r="DJ22" t="n">
-        <v>0.3225236382064094</v>
+        <v>0.1690998571180982</v>
       </c>
     </row>
     <row r="23">
@@ -8606,10 +8606,10 @@
         <v>0.3767806267806267</v>
       </c>
       <c r="DI23" t="n">
-        <v>0.6382433907099587</v>
+        <v>0.4177420708427303</v>
       </c>
       <c r="DJ23" t="n">
-        <v>0.2433513179787903</v>
+        <v>0.3385393957575134</v>
       </c>
     </row>
     <row r="24">
@@ -8952,10 +8952,10 @@
         <v>0.7004504504504503</v>
       </c>
       <c r="DI24" t="n">
-        <v>0.5293756601028387</v>
+        <v>0.3824579328591292</v>
       </c>
       <c r="DJ24" t="n">
-        <v>0.6060108249272838</v>
+        <v>0.6371260760420749</v>
       </c>
     </row>
     <row r="25">
@@ -9298,10 +9298,10 @@
         <v>0.4060283687943262</v>
       </c>
       <c r="DI25" t="n">
-        <v>0.4237140533040131</v>
+        <v>0.2606664748377865</v>
       </c>
       <c r="DJ25" t="n">
-        <v>0.2962035673585701</v>
+        <v>0.3574433642780199</v>
       </c>
     </row>
     <row r="26">
@@ -9644,10 +9644,10 @@
         <v>0.8257575757575757</v>
       </c>
       <c r="DI26" t="n">
-        <v>0.4888866659006271</v>
+        <v>0.4617177623492377</v>
       </c>
       <c r="DJ26" t="n">
-        <v>0.7915817495181655</v>
+        <v>0.782667076735775</v>
       </c>
     </row>
     <row r="27">
@@ -9990,10 +9990,10 @@
         <v>0.6412037037037036</v>
       </c>
       <c r="DI27" t="n">
-        <v>0.6382433907099588</v>
+        <v>0.4223998655195365</v>
       </c>
       <c r="DJ27" t="n">
-        <v>0.5588376175215569</v>
+        <v>0.6139514836696012</v>
       </c>
     </row>
     <row r="28">
@@ -10336,10 +10336,10 @@
         <v>0.6439393939393938</v>
       </c>
       <c r="DI28" t="n">
-        <v>0.4060151235862151</v>
+        <v>0.2295560820845411</v>
       </c>
       <c r="DJ28" t="n">
-        <v>0.5406232053469017</v>
+        <v>0.5676594864867252</v>
       </c>
     </row>
     <row r="29">
@@ -10682,10 +10682,10 @@
         <v>0.8397435897435899</v>
       </c>
       <c r="DI29" t="n">
-        <v>0.6237805698645743</v>
+        <v>0.5607576244668058</v>
       </c>
       <c r="DJ29" t="n">
-        <v>0.780584574704256</v>
+        <v>0.7972688119002851</v>
       </c>
     </row>
     <row r="30">
@@ -11028,10 +11028,10 @@
         <v>0.8704033214709372</v>
       </c>
       <c r="DI30" t="n">
-        <v>0.6540031179020298</v>
+        <v>0.5916890984027946</v>
       </c>
       <c r="DJ30" t="n">
-        <v>0.8025683739181378</v>
+        <v>0.8156267045248633</v>
       </c>
     </row>
     <row r="31">
@@ -11374,10 +11374,10 @@
         <v>0.4460784313725489</v>
       </c>
       <c r="DI31" t="n">
-        <v>0.5641045755770216</v>
+        <v>0.3589185414309656</v>
       </c>
       <c r="DJ31" t="n">
-        <v>0.3428191872739644</v>
+        <v>0.3974934268562424</v>
       </c>
     </row>
     <row r="32">
@@ -11720,10 +11720,10 @@
         <v>0.3694968553459118</v>
       </c>
       <c r="DI32" t="n">
-        <v>0.5804810523697456</v>
+        <v>0.476314548367589</v>
       </c>
       <c r="DJ32" t="n">
-        <v>0.2272723912285929</v>
+        <v>0.314762038641579</v>
       </c>
     </row>
     <row r="33">
@@ -12066,10 +12066,10 @@
         <v>0.6388888888888887</v>
       </c>
       <c r="DI33" t="n">
-        <v>0.5265370117756769</v>
+        <v>0.3334027012920932</v>
       </c>
       <c r="DJ33" t="n">
-        <v>0.5489521561849215</v>
+        <v>0.5810590199750186</v>
       </c>
     </row>
     <row r="34">
@@ -12412,10 +12412,10 @@
         <v>0.9246580605501767</v>
       </c>
       <c r="DI34" t="n">
-        <v>0.7373060466579069</v>
+        <v>0.6507095870028997</v>
       </c>
       <c r="DJ34" t="n">
-        <v>0.8585399825559648</v>
+        <v>0.8792836659605621</v>
       </c>
     </row>
     <row r="35">
@@ -12758,10 +12758,10 @@
         <v>0.2959770114942527</v>
       </c>
       <c r="DI35" t="n">
-        <v>0.6021471943061953</v>
+        <v>0.5218550294966274</v>
       </c>
       <c r="DJ35" t="n">
-        <v>0.2299957505159447</v>
+        <v>0.2472172664004959</v>
       </c>
     </row>
     <row r="36">
@@ -13104,10 +13104,10 @@
         <v>0.1149940262843488</v>
       </c>
       <c r="DI36" t="n">
-        <v>0.6596274547596516</v>
+        <v>0.5721190533169263</v>
       </c>
       <c r="DJ36" t="n">
-        <v>0.2432368215259753</v>
+        <v>0.09388751159653928</v>
       </c>
     </row>
     <row r="37">
@@ -13450,10 +13450,10 @@
         <v>0.06798941798941784</v>
       </c>
       <c r="DI37" t="n">
-        <v>0.7188701761608096</v>
+        <v>0.6191236616118571</v>
       </c>
       <c r="DJ37" t="n">
-        <v>0.2635490147638415</v>
+        <v>0.1101912844320542</v>
       </c>
     </row>
     <row r="38">
@@ -13796,10 +13796,10 @@
         <v>0.7427536231884059</v>
       </c>
       <c r="DI38" t="n">
-        <v>0.4449038136104542</v>
+        <v>0.3910997083643615</v>
       </c>
       <c r="DJ38" t="n">
-        <v>0.6953437930210906</v>
+        <v>0.7169924973213386</v>
       </c>
     </row>
     <row r="39">
@@ -14142,10 +14142,10 @@
         <v>0.4963768115942025</v>
       </c>
       <c r="DI39" t="n">
-        <v>0.5842127273112365</v>
+        <v>0.5088336526733112</v>
       </c>
       <c r="DJ39" t="n">
-        <v>0.3901845400801141</v>
+        <v>0.4488765552923529</v>
       </c>
     </row>
     <row r="40">
@@ -14488,10 +14488,10 @@
         <v>0.7023809523809522</v>
       </c>
       <c r="DI40" t="n">
-        <v>0.4386547768306817</v>
+        <v>0.315979719952345</v>
       </c>
       <c r="DJ40" t="n">
-        <v>0.609436769180295</v>
+        <v>0.6388818373951262</v>
       </c>
     </row>
     <row r="41">
@@ -14834,10 +14834,10 @@
         <v>0.4743589743589742</v>
       </c>
       <c r="DI41" t="n">
-        <v>0.468579563771122</v>
+        <v>0.2831266862273459</v>
       </c>
       <c r="DJ41" t="n">
-        <v>0.3623793574319543</v>
+        <v>0.4202794643481624</v>
       </c>
     </row>
     <row r="42">
@@ -15180,10 +15180,10 @@
         <v>0.6337719298245614</v>
       </c>
       <c r="DI42" t="n">
-        <v>0.4994101508716062</v>
+        <v>0.3129098825484668</v>
       </c>
       <c r="DJ42" t="n">
-        <v>0.5226211977612119</v>
+        <v>0.5691883729648198</v>
       </c>
     </row>
     <row r="43">
@@ -15526,10 +15526,10 @@
         <v>0.7091194968553457</v>
       </c>
       <c r="DI43" t="n">
-        <v>0.3647347840379033</v>
+        <v>0.3123832008698312</v>
       </c>
       <c r="DJ43" t="n">
-        <v>0.6301697284306647</v>
+        <v>0.655899597427451</v>
       </c>
     </row>
     <row r="44">
@@ -15872,10 +15872,10 @@
         <v>0.4495133819951337</v>
       </c>
       <c r="DI44" t="n">
-        <v>0.281095269282879</v>
+        <v>0.2418578148526029</v>
       </c>
       <c r="DJ44" t="n">
-        <v>0.3347761707638779</v>
+        <v>0.3858735944699245</v>
       </c>
     </row>
     <row r="45">
@@ -16218,10 +16218,10 @@
         <v>0.7007392768262332</v>
       </c>
       <c r="DI45" t="n">
-        <v>0.5972463933414922</v>
+        <v>0.4221068334767851</v>
       </c>
       <c r="DJ45" t="n">
-        <v>0.5900871531932576</v>
+        <v>0.6547708122217322</v>
       </c>
     </row>
     <row r="46">
@@ -16564,10 +16564,10 @@
         <v>0.07598039215686306</v>
       </c>
       <c r="DI46" t="n">
-        <v>0.8536439508131846</v>
+        <v>0.7260564347211008</v>
       </c>
       <c r="DJ46" t="n">
-        <v>0.3324237608476598</v>
+        <v>0.1763868595859825</v>
       </c>
     </row>
     <row r="47">
@@ -16910,10 +16910,10 @@
         <v>0.05817610062893063</v>
       </c>
       <c r="DI47" t="n">
-        <v>0.7259938612813154</v>
+        <v>0.6250167644696017</v>
       </c>
       <c r="DJ47" t="n">
-        <v>0.2230010567956715</v>
+        <v>0.07148792438914692</v>
       </c>
     </row>
     <row r="48">
@@ -17256,10 +17256,10 @@
         <v>0.814625850340136</v>
       </c>
       <c r="DI48" t="n">
-        <v>0.2973550493943929</v>
+        <v>0.2305089116825934</v>
       </c>
       <c r="DJ48" t="n">
-        <v>0.7717839702836753</v>
+        <v>0.7660408458238296</v>
       </c>
     </row>
     <row r="49">
@@ -17602,10 +17602,10 @@
         <v>0.8980099502487562</v>
       </c>
       <c r="DI49" t="n">
-        <v>0.3993770922128492</v>
+        <v>0.4001572373178563</v>
       </c>
       <c r="DJ49" t="n">
-        <v>0.8669926545774052</v>
+        <v>0.847456764659791</v>
       </c>
     </row>
     <row r="50">
@@ -17948,10 +17948,10 @@
         <v>0.6370370370370371</v>
       </c>
       <c r="DI50" t="n">
-        <v>0.6111120123245234</v>
+        <v>0.4750378597862706</v>
       </c>
       <c r="DJ50" t="n">
-        <v>0.5283348701431939</v>
+        <v>0.5996554165968405</v>
       </c>
     </row>
     <row r="51">
@@ -18294,10 +18294,10 @@
         <v>0.5126262626262627</v>
       </c>
       <c r="DI51" t="n">
-        <v>0.2841671987229992</v>
+        <v>0.2264366063772733</v>
       </c>
       <c r="DJ51" t="n">
-        <v>0.3986379954619315</v>
+        <v>0.4567209030995519</v>
       </c>
     </row>
     <row r="52">
@@ -18640,10 +18640,10 @@
         <v>0.02668845315904158</v>
       </c>
       <c r="DI52" t="n">
-        <v>0.7764160183830416</v>
+        <v>0.6612104963457507</v>
       </c>
       <c r="DJ52" t="n">
-        <v>0.2917484562876466</v>
+        <v>0.1151123497820608</v>
       </c>
     </row>
     <row r="53">
@@ -18986,10 +18986,10 @@
         <v>0.8390269151138714</v>
       </c>
       <c r="DI53" t="n">
-        <v>0.4476944912897998</v>
+        <v>0.4823532754359408</v>
       </c>
       <c r="DJ53" t="n">
-        <v>0.7606495849740854</v>
+        <v>0.7762656066219911</v>
       </c>
     </row>
     <row r="54">
@@ -19332,10 +19332,10 @@
         <v>0.7677304964539009</v>
       </c>
       <c r="DI54" t="n">
-        <v>0.3700817189525266</v>
+        <v>0.3272883619623906</v>
       </c>
       <c r="DJ54" t="n">
-        <v>0.724042072936202</v>
+        <v>0.7246399974320996</v>
       </c>
     </row>
     <row r="55">
@@ -19678,10 +19678,10 @@
         <v>0.9075757575757575</v>
       </c>
       <c r="DI55" t="n">
-        <v>0.4100153730818366</v>
+        <v>0.3181613438458528</v>
       </c>
       <c r="DJ55" t="n">
-        <v>0.8489566844425108</v>
+        <v>0.8362634803321783</v>
       </c>
     </row>
     <row r="56">
@@ -20024,10 +20024,10 @@
         <v>0.6758373205741625</v>
       </c>
       <c r="DI56" t="n">
-        <v>0.5114945441053979</v>
+        <v>0.4244258866409357</v>
       </c>
       <c r="DJ56" t="n">
-        <v>0.5702729927087606</v>
+        <v>0.6049871536687653</v>
       </c>
     </row>
     <row r="57">
@@ -20370,10 +20370,10 @@
         <v>0.562962962962963</v>
       </c>
       <c r="DI57" t="n">
-        <v>0.5135424127940307</v>
+        <v>0.356331184297787</v>
       </c>
       <c r="DJ57" t="n">
-        <v>0.5092534881442331</v>
+        <v>0.5471246839752645</v>
       </c>
     </row>
     <row r="58">
@@ -20716,10 +20716,10 @@
         <v>0.4249539594843461</v>
       </c>
       <c r="DI58" t="n">
-        <v>0.3268566926678907</v>
+        <v>0.3124136360566764</v>
       </c>
       <c r="DJ58" t="n">
-        <v>0.2894878697484925</v>
+        <v>0.3663840999177265</v>
       </c>
     </row>
     <row r="59">
@@ -21062,10 +21062,10 @@
         <v>0.2499999999999998</v>
       </c>
       <c r="DI59" t="n">
-        <v>0.5081040402786321</v>
+        <v>0.4520186078147881</v>
       </c>
       <c r="DJ59" t="n">
-        <v>0.2215945910956589</v>
+        <v>0.2014149954836934</v>
       </c>
     </row>
     <row r="60">
@@ -21408,10 +21408,10 @@
         <v>0.2962962962962962</v>
       </c>
       <c r="DI60" t="n">
-        <v>0.4753496898467598</v>
+        <v>0.3697730122612077</v>
       </c>
       <c r="DJ60" t="n">
-        <v>0.2805383693729336</v>
+        <v>0.2804580173085978</v>
       </c>
     </row>
     <row r="61">
@@ -21754,10 +21754,10 @@
         <v>0.2227891156462586</v>
       </c>
       <c r="DI61" t="n">
-        <v>0.6299985563565662</v>
+        <v>0.5451584417210836</v>
       </c>
       <c r="DJ61" t="n">
-        <v>0.2213661335221531</v>
+        <v>0.1834540552283858</v>
       </c>
     </row>
     <row r="62">
@@ -22100,10 +22100,10 @@
         <v>0.02604166666666677</v>
       </c>
       <c r="DI62" t="n">
-        <v>0.7250594433169968</v>
+        <v>0.6240343758975713</v>
       </c>
       <c r="DJ62" t="n">
-        <v>0.2612496943768693</v>
+        <v>0.08398948473771711</v>
       </c>
     </row>
     <row r="63">
@@ -22446,10 +22446,10 @@
         <v>0.09062253743104796</v>
       </c>
       <c r="DI63" t="n">
-        <v>0.6930755772584281</v>
+        <v>0.5951115035571459</v>
       </c>
       <c r="DJ63" t="n">
-        <v>0.3021884128311983</v>
+        <v>0.1202261868653769</v>
       </c>
     </row>
     <row r="64">
@@ -22792,10 +22792,10 @@
         <v>0.6354166666666666</v>
       </c>
       <c r="DI64" t="n">
-        <v>0.430062619639096</v>
+        <v>0.2902181939927814</v>
       </c>
       <c r="DJ64" t="n">
-        <v>0.5579433464134559</v>
+        <v>0.5978801784807587</v>
       </c>
     </row>
     <row r="65">
@@ -23138,10 +23138,10 @@
         <v>0.4569388665774206</v>
       </c>
       <c r="DI65" t="n">
-        <v>0.5121243341057826</v>
+        <v>0.3553251480804833</v>
       </c>
       <c r="DJ65" t="n">
-        <v>0.370076992216375</v>
+        <v>0.4327970366995269</v>
       </c>
     </row>
     <row r="66">
@@ -23484,10 +23484,10 @@
         <v>0.04629629629629631</v>
       </c>
       <c r="DI66" t="n">
-        <v>0.7965765733753316</v>
+        <v>0.6807777969502029</v>
       </c>
       <c r="DJ66" t="n">
-        <v>0.3158090893657367</v>
+        <v>0.1311082218150844</v>
       </c>
     </row>
     <row r="67">
@@ -23830,10 +23830,10 @@
         <v>0.1955211024978464</v>
       </c>
       <c r="DI67" t="n">
-        <v>0.5504417099023508</v>
+        <v>0.485610339080938</v>
       </c>
       <c r="DJ67" t="n">
-        <v>0.2853159552454234</v>
+        <v>0.179682823510148</v>
       </c>
     </row>
     <row r="68">
@@ -24176,10 +24176,10 @@
         <v>0.04629629629629665</v>
       </c>
       <c r="DI68" t="n">
-        <v>0.7661639784683356</v>
+        <v>0.6564697342222311</v>
       </c>
       <c r="DJ68" t="n">
-        <v>0.3079446720700444</v>
+        <v>0.1241077279809608</v>
       </c>
     </row>
     <row r="69">
@@ -24522,10 +24522,10 @@
         <v>0.05370370370370354</v>
       </c>
       <c r="DI69" t="n">
-        <v>0.7946349977007656</v>
+        <v>0.6834093758975713</v>
       </c>
       <c r="DJ69" t="n">
-        <v>0.2802712482972228</v>
+        <v>0.1327984872550846</v>
       </c>
     </row>
     <row r="70">
@@ -24868,10 +24868,10 @@
         <v>0.7546296296296298</v>
       </c>
       <c r="DI70" t="n">
-        <v>0.5088351107178419</v>
+        <v>0.4109754847618769</v>
       </c>
       <c r="DJ70" t="n">
-        <v>0.7289158849496207</v>
+        <v>0.738791350641931</v>
       </c>
     </row>
     <row r="71">
@@ -25214,10 +25214,10 @@
         <v>0.03079242032730429</v>
       </c>
       <c r="DI71" t="n">
-        <v>0.7898123804672214</v>
+        <v>0.6755328197010931</v>
       </c>
       <c r="DJ71" t="n">
-        <v>0.2943386975691636</v>
+        <v>0.1294762348709801</v>
       </c>
     </row>
     <row r="72">
@@ -25560,10 +25560,10 @@
         <v>0.1263631406761176</v>
       </c>
       <c r="DI72" t="n">
-        <v>0.8315445509746356</v>
+        <v>0.6950946188605088</v>
       </c>
       <c r="DJ72" t="n">
-        <v>0.2895295038316317</v>
+        <v>0.140049324420084</v>
       </c>
     </row>
     <row r="73">
@@ -25906,10 +25906,10 @@
         <v>0.06113636363636345</v>
       </c>
       <c r="DI73" t="n">
-        <v>0.7931403667395385</v>
+        <v>0.6684206556975836</v>
       </c>
       <c r="DJ73" t="n">
-        <v>0.2704011611053865</v>
+        <v>0.1173864727774023</v>
       </c>
     </row>
     <row r="74">
@@ -26252,10 +26252,10 @@
         <v>0.06300576163656386</v>
       </c>
       <c r="DI74" t="n">
-        <v>0.8251072643794083</v>
+        <v>0.6994221939204885</v>
       </c>
       <c r="DJ74" t="n">
-        <v>0.3106273415347734</v>
+        <v>0.1552936237520109</v>
       </c>
     </row>
     <row r="75">
@@ -26598,10 +26598,10 @@
         <v>0.8390882803197823</v>
       </c>
       <c r="DI75" t="n">
-        <v>0.8116628893367726</v>
+        <v>0.7991451356532193</v>
       </c>
       <c r="DJ75" t="n">
-        <v>0.7596671919020944</v>
+        <v>0.7919154817473382</v>
       </c>
     </row>
     <row r="76">
@@ -26944,10 +26944,10 @@
         <v>0.7042951756126793</v>
       </c>
       <c r="DI76" t="n">
-        <v>0.7329042758537887</v>
+        <v>0.6566865408942568</v>
       </c>
       <c r="DJ76" t="n">
-        <v>0.6211163901613654</v>
+        <v>0.6458352615352541</v>
       </c>
     </row>
     <row r="77">
@@ -27290,10 +27290,10 @@
         <v>0.9828989305764533</v>
       </c>
       <c r="DI77" t="n">
-        <v>0.9652655414035184</v>
+        <v>0.9673582231390903</v>
       </c>
       <c r="DJ77" t="n">
-        <v>0.9391918444002871</v>
+        <v>0.956287740349565</v>
       </c>
     </row>
     <row r="78">
@@ -27636,10 +27636,10 @@
         <v>0.3691908905758191</v>
       </c>
       <c r="DI78" t="n">
-        <v>0.8032914837368291</v>
+        <v>0.6652604098839565</v>
       </c>
       <c r="DJ78" t="n">
-        <v>0.2623635727548937</v>
+        <v>0.3395510221412917</v>
       </c>
     </row>
     <row r="79">
@@ -27982,10 +27982,10 @@
         <v>0.08266930048105371</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.8598881101264727</v>
+        <v>0.73101070177215</v>
       </c>
       <c r="DJ79" t="n">
-        <v>0.3380839359685767</v>
+        <v>0.1813411266370316</v>
       </c>
     </row>
     <row r="80">
@@ -28328,10 +28328,10 @@
         <v>0.2878280466742489</v>
       </c>
       <c r="DI80" t="n">
-        <v>0.585382345706969</v>
+        <v>0.5053080590929984</v>
       </c>
       <c r="DJ80" t="n">
-        <v>0.1950144753949476</v>
+        <v>0.2145261427720901</v>
       </c>
     </row>
     <row r="81">
@@ -28674,10 +28674,10 @@
         <v>0.1223458984192313</v>
       </c>
       <c r="DI81" t="n">
-        <v>0.8088833954989182</v>
+        <v>0.6884774097542743</v>
       </c>
       <c r="DJ81" t="n">
-        <v>0.2669502816161595</v>
+        <v>0.1105349588999806</v>
       </c>
     </row>
     <row r="82">
@@ -29020,10 +29020,10 @@
         <v>0.2162378751925396</v>
       </c>
       <c r="DI82" t="n">
-        <v>0.7086022605558421</v>
+        <v>0.6067192176329703</v>
       </c>
       <c r="DJ82" t="n">
-        <v>0.1991424096247628</v>
+        <v>0.1588376376044736</v>
       </c>
     </row>
     <row r="83">
@@ -29366,10 +29366,10 @@
         <v>0.7694372371835019</v>
       </c>
       <c r="DI83" t="n">
-        <v>0.7780572187107833</v>
+        <v>0.7318495315684566</v>
       </c>
       <c r="DJ83" t="n">
-        <v>0.6807214846340734</v>
+        <v>0.7309591052253744</v>
       </c>
     </row>
     <row r="84">
@@ -29712,10 +29712,10 @@
         <v>0.09269821812086007</v>
       </c>
       <c r="DI84" t="n">
-        <v>0.7716909650360607</v>
+        <v>0.6599698079290985</v>
       </c>
       <c r="DJ84" t="n">
-        <v>0.2596304905186314</v>
+        <v>0.08170919421646668</v>
       </c>
     </row>
     <row r="85">
@@ -30058,10 +30058,10 @@
         <v>0.62281011259636</v>
       </c>
       <c r="DI85" t="n">
-        <v>0.5833454272438099</v>
+        <v>0.4424710809958134</v>
       </c>
       <c r="DJ85" t="n">
-        <v>0.5025519646264477</v>
+        <v>0.5545083931542631</v>
       </c>
     </row>
     <row r="86">
@@ -30404,10 +30404,10 @@
         <v>0.2302070645554201</v>
       </c>
       <c r="DI86" t="n">
-        <v>0.8190211637217893</v>
+        <v>0.7008211621578935</v>
       </c>
       <c r="DJ86" t="n">
-        <v>0.2870407806442672</v>
+        <v>0.2047714235043131</v>
       </c>
     </row>
     <row r="87">
@@ -30750,10 +30750,10 @@
         <v>0.07909923472588114</v>
       </c>
       <c r="DI87" t="n">
-        <v>0.8498200779465911</v>
+        <v>0.720378506991998</v>
       </c>
       <c r="DJ87" t="n">
-        <v>0.3015373826382874</v>
+        <v>0.1558540693708217</v>
       </c>
     </row>
     <row r="88">
@@ -31096,10 +31096,10 @@
         <v>0.4547110912120985</v>
       </c>
       <c r="DI88" t="n">
-        <v>0.687346320715402</v>
+        <v>0.5696844781410231</v>
       </c>
       <c r="DJ88" t="n">
-        <v>0.2920741616348765</v>
+        <v>0.3916611858176881</v>
       </c>
     </row>
     <row r="89">
@@ -31442,10 +31442,10 @@
         <v>0.09227055285400561</v>
       </c>
       <c r="DI89" t="n">
-        <v>0.7697394235142676</v>
+        <v>0.6543892499367459</v>
       </c>
       <c r="DJ89" t="n">
-        <v>0.2749633928515838</v>
+        <v>0.0891362378125284</v>
       </c>
     </row>
     <row r="90">
@@ -31788,10 +31788,10 @@
         <v>0.07086663792636357</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.8375639796283092</v>
+        <v>0.7136863225527214</v>
       </c>
       <c r="DJ90" t="n">
-        <v>0.3079892723302376</v>
+        <v>0.1558984209107271</v>
       </c>
     </row>
     <row r="91">
@@ -32134,10 +32134,10 @@
         <v>0.1678164155990426</v>
       </c>
       <c r="DI91" t="n">
-        <v>0.8400418919522978</v>
+        <v>0.7085254019681272</v>
       </c>
       <c r="DJ91" t="n">
-        <v>0.2903690944826552</v>
+        <v>0.1355036433449252</v>
       </c>
     </row>
     <row r="92">
@@ -32480,10 +32480,10 @@
         <v>0.938369459721773</v>
       </c>
       <c r="DI92" t="n">
-        <v>0.9004575693443317</v>
+        <v>0.9065692216750525</v>
       </c>
       <c r="DJ92" t="n">
-        <v>0.8853057553059356</v>
+        <v>0.8995712722373003</v>
       </c>
     </row>
     <row r="93">
@@ -32826,10 +32826,10 @@
         <v>0.1390512303161015</v>
       </c>
       <c r="DI93" t="n">
-        <v>0.7540059517295651</v>
+        <v>0.6362681640905185</v>
       </c>
       <c r="DJ93" t="n">
-        <v>0.2045782828331663</v>
+        <v>0.09188356916539568</v>
       </c>
     </row>
     <row r="94">
@@ -33172,10 +33172,10 @@
         <v>0.3998845411412387</v>
       </c>
       <c r="DI94" t="n">
-        <v>0.7436808235091117</v>
+        <v>0.620046817625555</v>
       </c>
       <c r="DJ94" t="n">
-        <v>0.273912995986782</v>
+        <v>0.3388353588200513</v>
       </c>
     </row>
     <row r="95">
@@ -33518,10 +33518,10 @@
         <v>0.1445580549875028</v>
       </c>
       <c r="DI95" t="n">
-        <v>0.762540808025799</v>
+        <v>0.6338552997101233</v>
       </c>
       <c r="DJ95" t="n">
-        <v>0.2586912322008871</v>
+        <v>0.08391688406131999</v>
       </c>
     </row>
     <row r="96">
@@ -33864,10 +33864,10 @@
         <v>0.5981281350331707</v>
       </c>
       <c r="DI96" t="n">
-        <v>0.667198035271151</v>
+        <v>0.5670650263122676</v>
       </c>
       <c r="DJ96" t="n">
-        <v>0.4998440089510464</v>
+        <v>0.5385823973663532</v>
       </c>
     </row>
     <row r="97">
@@ -34210,10 +34210,10 @@
         <v>0.04414123648790737</v>
       </c>
       <c r="DI97" t="n">
-        <v>0.8041373083026447</v>
+        <v>0.684704274407879</v>
       </c>
       <c r="DJ97" t="n">
-        <v>0.2728268179141453</v>
+        <v>0.1138671600000108</v>
       </c>
     </row>
     <row r="98">
@@ -34556,10 +34556,10 @@
         <v>0.9617228507001686</v>
       </c>
       <c r="DI98" t="n">
-        <v>0.9319399589103291</v>
+        <v>0.9270763232978396</v>
       </c>
       <c r="DJ98" t="n">
-        <v>0.9113078247071006</v>
+        <v>0.9317456820826514</v>
       </c>
     </row>
     <row r="99">
@@ -34902,10 +34902,10 @@
         <v>0.1491852494956827</v>
       </c>
       <c r="DI99" t="n">
-        <v>0.8050033577445868</v>
+        <v>0.6885622781664629</v>
       </c>
       <c r="DJ99" t="n">
-        <v>0.2685262337429998</v>
+        <v>0.1109058878210318</v>
       </c>
     </row>
     <row r="100">
@@ -35248,10 +35248,10 @@
         <v>0.6210135663044252</v>
       </c>
       <c r="DI100" t="n">
-        <v>0.6539044287891452</v>
+        <v>0.5595195099378153</v>
       </c>
       <c r="DJ100" t="n">
-        <v>0.4997037282865862</v>
+        <v>0.5447803893840825</v>
       </c>
     </row>
     <row r="101">
@@ -35594,10 +35594,10 @@
         <v>0.8101765745907098</v>
       </c>
       <c r="DI101" t="n">
-        <v>0.7504234867494997</v>
+        <v>0.75403475824413</v>
       </c>
       <c r="DJ101" t="n">
-        <v>0.7472607827516454</v>
+        <v>0.7480113381847038</v>
       </c>
     </row>
     <row r="102">
@@ -35940,10 +35940,10 @@
         <v>0.1690867317421888</v>
       </c>
       <c r="DI102" t="n">
-        <v>0.7582071258656267</v>
+        <v>0.6495742375023035</v>
       </c>
       <c r="DJ102" t="n">
-        <v>0.2480529142280245</v>
+        <v>0.1152083335316573</v>
       </c>
     </row>
     <row r="103">
@@ -36286,10 +36286,10 @@
         <v>0.277106227106227</v>
       </c>
       <c r="DI103" t="n">
-        <v>0.4116145960958516</v>
+        <v>0.3752009176891131</v>
       </c>
       <c r="DJ103" t="n">
-        <v>0.2332598144624723</v>
+        <v>0.2296201236888218</v>
       </c>
     </row>
     <row r="104">
@@ -36632,10 +36632,10 @@
         <v>0.9488784559207095</v>
       </c>
       <c r="DI104" t="n">
-        <v>0.6168837304729783</v>
+        <v>0.581274832744944</v>
       </c>
       <c r="DJ104" t="n">
-        <v>0.9371952881682651</v>
+        <v>0.9121686735877003</v>
       </c>
     </row>
     <row r="105">
@@ -36978,10 +36978,10 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="DI105" t="n">
-        <v>0.4591156383799239</v>
+        <v>0.2892736032130635</v>
       </c>
       <c r="DJ105" t="n">
-        <v>0.5885212545047881</v>
+        <v>0.6081611008680131</v>
       </c>
     </row>
     <row r="106">
@@ -37324,10 +37324,10 @@
         <v>0.322327044025157</v>
       </c>
       <c r="DI106" t="n">
-        <v>0.4261445918378359</v>
+        <v>0.3807397818189809</v>
       </c>
       <c r="DJ106" t="n">
-        <v>0.2324369386328306</v>
+        <v>0.2782952314959878</v>
       </c>
     </row>
     <row r="107">
@@ -37670,10 +37670,10 @@
         <v>0.8578431372549019</v>
       </c>
       <c r="DI107" t="n">
-        <v>0.770540349481692</v>
+        <v>0.8141721274604552</v>
       </c>
       <c r="DJ107" t="n">
-        <v>0.8025572253574282</v>
+        <v>0.7929602171344868</v>
       </c>
     </row>
     <row r="108">
@@ -38016,10 +38016,10 @@
         <v>0.351171458998935</v>
       </c>
       <c r="DI108" t="n">
-        <v>0.428173939367775</v>
+        <v>0.311266034154866</v>
       </c>
       <c r="DJ108" t="n">
-        <v>0.235770039159101</v>
+        <v>0.3080809599771341</v>
       </c>
     </row>
     <row r="109">
@@ -38362,10 +38362,10 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="DI109" t="n">
-        <v>0.4982034065699665</v>
+        <v>0.3112887544084253</v>
       </c>
       <c r="DJ109" t="n">
-        <v>0.3154270296153226</v>
+        <v>0.3735761676448657</v>
       </c>
     </row>
     <row r="110">
@@ -38708,10 +38708,10 @@
         <v>0.1898625429553265</v>
       </c>
       <c r="DI110" t="n">
-        <v>0.663406058896421</v>
+        <v>0.5751292386936779</v>
       </c>
       <c r="DJ110" t="n">
-        <v>0.2222914789436459</v>
+        <v>0.1344216727812139</v>
       </c>
     </row>
     <row r="111">
@@ -39054,10 +39054,10 @@
         <v>0.1525270316551688</v>
       </c>
       <c r="DI111" t="n">
-        <v>0.6081754266667971</v>
+        <v>0.5312957695567525</v>
       </c>
       <c r="DJ111" t="n">
-        <v>0.3012022588271058</v>
+        <v>0.1366887526674703</v>
       </c>
     </row>
     <row r="112">
@@ -39400,10 +39400,10 @@
         <v>0</v>
       </c>
       <c r="DI112" t="n">
-        <v>0.7578813145998073</v>
+        <v>0.650076042564238</v>
       </c>
       <c r="DJ112" t="n">
-        <v>0.2619232671545096</v>
+        <v>0.1004064674291194</v>
       </c>
     </row>
     <row r="113">
@@ -39413,343 +39413,343 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.2810952692828789</v>
+        <v>0.08815737600805186</v>
       </c>
       <c r="C113" t="n">
-        <v>0.9199561201605272</v>
+        <v>0.9328578615307622</v>
       </c>
       <c r="D113" t="n">
-        <v>0.63353608863377</v>
+        <v>0.4789075200208932</v>
       </c>
       <c r="E113" t="n">
-        <v>0.5310608484754228</v>
+        <v>0.3905256701093761</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2797910340899978</v>
+        <v>0.1258144391887106</v>
       </c>
       <c r="G113" t="n">
-        <v>0.4581229828265522</v>
+        <v>0.3393606001936521</v>
       </c>
       <c r="H113" t="n">
-        <v>0.6067343942784607</v>
+        <v>0.3854181526823103</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5292392949469377</v>
+        <v>0.3359133790330499</v>
       </c>
       <c r="J113" t="n">
-        <v>0.6299933119085522</v>
+        <v>0.5404155559736292</v>
       </c>
       <c r="K113" t="n">
-        <v>0.6089326963550769</v>
+        <v>0.399144051566048</v>
       </c>
       <c r="L113" t="n">
-        <v>0.7810668821859362</v>
+        <v>0.6682940585465554</v>
       </c>
       <c r="M113" t="n">
-        <v>0.6012785015129102</v>
+        <v>0.3897405983996379</v>
       </c>
       <c r="N113" t="n">
-        <v>0.7207853862894091</v>
+        <v>0.6465534591857616</v>
       </c>
       <c r="O113" t="n">
-        <v>0.5091730472609882</v>
+        <v>0.5072332325003721</v>
       </c>
       <c r="P113" t="n">
-        <v>0.6870971842911479</v>
+        <v>0.6198244247721296</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.4679244910802386</v>
+        <v>0.2826069357075954</v>
       </c>
       <c r="R113" t="n">
-        <v>0.5835532910326737</v>
+        <v>0.4632787697001843</v>
       </c>
       <c r="S113" t="n">
-        <v>0.5791640224008996</v>
+        <v>0.5245112663737305</v>
       </c>
       <c r="T113" t="n">
-        <v>0.697810125671108</v>
+        <v>0.6025332098101377</v>
       </c>
       <c r="U113" t="n">
-        <v>0.8047408477543434</v>
+        <v>0.6872555297437253</v>
       </c>
       <c r="V113" t="n">
-        <v>0.8403877870396534</v>
+        <v>0.7197107457605849</v>
       </c>
       <c r="W113" t="n">
-        <v>0.6382433907099587</v>
+        <v>0.4177420708427303</v>
       </c>
       <c r="X113" t="n">
-        <v>0.5293756601028387</v>
+        <v>0.3824579328591292</v>
       </c>
       <c r="Y113" t="n">
-        <v>0.4237140533040131</v>
+        <v>0.2606664748377865</v>
       </c>
       <c r="Z113" t="n">
-        <v>0.4888866659006271</v>
+        <v>0.4617177623492377</v>
       </c>
       <c r="AA113" t="n">
-        <v>0.6382433907099588</v>
+        <v>0.4223998655195365</v>
       </c>
       <c r="AB113" t="n">
-        <v>0.4060151235862151</v>
+        <v>0.2295560820845411</v>
       </c>
       <c r="AC113" t="n">
-        <v>0.6237805698645743</v>
+        <v>0.5607576244668058</v>
       </c>
       <c r="AD113" t="n">
-        <v>0.6540031179020298</v>
+        <v>0.5916890984027946</v>
       </c>
       <c r="AE113" t="n">
-        <v>0.5641045755770216</v>
+        <v>0.3589185414309656</v>
       </c>
       <c r="AF113" t="n">
-        <v>0.5804810523697456</v>
+        <v>0.476314548367589</v>
       </c>
       <c r="AG113" t="n">
-        <v>0.5265370117756769</v>
+        <v>0.3334027012920932</v>
       </c>
       <c r="AH113" t="n">
-        <v>0.7373060466579069</v>
+        <v>0.6507095870028997</v>
       </c>
       <c r="AI113" t="n">
-        <v>0.6021471943061953</v>
+        <v>0.5218550294966274</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.6596274547596516</v>
+        <v>0.5721190533169263</v>
       </c>
       <c r="AK113" t="n">
-        <v>0.7188701761608096</v>
+        <v>0.6191236616118571</v>
       </c>
       <c r="AL113" t="n">
-        <v>0.4449038136104542</v>
+        <v>0.3910997083643615</v>
       </c>
       <c r="AM113" t="n">
-        <v>0.5842127273112365</v>
+        <v>0.5088336526733112</v>
       </c>
       <c r="AN113" t="n">
-        <v>0.4386547768306817</v>
+        <v>0.315979719952345</v>
       </c>
       <c r="AO113" t="n">
-        <v>0.468579563771122</v>
+        <v>0.2831266862273459</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.4994101508716062</v>
+        <v>0.3129098825484668</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.3647347840379033</v>
+        <v>0.3123832008698312</v>
       </c>
       <c r="AR113" t="n">
-        <v>0.281095269282879</v>
+        <v>0.2418578148526029</v>
       </c>
       <c r="AS113" t="n">
-        <v>0.5972463933414922</v>
+        <v>0.4221068334767851</v>
       </c>
       <c r="AT113" t="n">
-        <v>0.8536439508131846</v>
+        <v>0.7260564347211008</v>
       </c>
       <c r="AU113" t="n">
-        <v>0.7259938612813154</v>
+        <v>0.6250167644696017</v>
       </c>
       <c r="AV113" t="n">
-        <v>0.2973550493943929</v>
+        <v>0.2305089116825934</v>
       </c>
       <c r="AW113" t="n">
-        <v>0.3993770922128492</v>
+        <v>0.4001572373178563</v>
       </c>
       <c r="AX113" t="n">
-        <v>0.6111120123245234</v>
+        <v>0.4750378597862706</v>
       </c>
       <c r="AY113" t="n">
-        <v>0.2841671987229992</v>
+        <v>0.2264366063772733</v>
       </c>
       <c r="AZ113" t="n">
-        <v>0.7764160183830416</v>
+        <v>0.6612104963457507</v>
       </c>
       <c r="BA113" t="n">
-        <v>0.4476944912897998</v>
+        <v>0.4823532754359408</v>
       </c>
       <c r="BB113" t="n">
-        <v>0.3700817189525266</v>
+        <v>0.3272883619623906</v>
       </c>
       <c r="BC113" t="n">
-        <v>0.4100153730818366</v>
+        <v>0.3181613438458528</v>
       </c>
       <c r="BD113" t="n">
-        <v>0.5114945441053979</v>
+        <v>0.4244258866409357</v>
       </c>
       <c r="BE113" t="n">
-        <v>0.5135424127940307</v>
+        <v>0.356331184297787</v>
       </c>
       <c r="BF113" t="n">
-        <v>0.3268566926678907</v>
+        <v>0.3124136360566764</v>
       </c>
       <c r="BG113" t="n">
-        <v>0.5081040402786321</v>
+        <v>0.4520186078147881</v>
       </c>
       <c r="BH113" t="n">
-        <v>0.4753496898467598</v>
+        <v>0.3697730122612077</v>
       </c>
       <c r="BI113" t="n">
-        <v>0.6299985563565662</v>
+        <v>0.5451584417210836</v>
       </c>
       <c r="BJ113" t="n">
-        <v>0.7250594433169968</v>
+        <v>0.6240343758975713</v>
       </c>
       <c r="BK113" t="n">
-        <v>0.6930755772584281</v>
+        <v>0.5951115035571459</v>
       </c>
       <c r="BL113" t="n">
-        <v>0.430062619639096</v>
+        <v>0.2902181939927814</v>
       </c>
       <c r="BM113" t="n">
-        <v>0.5121243341057826</v>
+        <v>0.3553251480804833</v>
       </c>
       <c r="BN113" t="n">
-        <v>0.7965765733753316</v>
+        <v>0.6807777969502029</v>
       </c>
       <c r="BO113" t="n">
-        <v>0.5504417099023508</v>
+        <v>0.485610339080938</v>
       </c>
       <c r="BP113" t="n">
-        <v>0.7661639784683356</v>
+        <v>0.6564697342222311</v>
       </c>
       <c r="BQ113" t="n">
-        <v>0.7946349977007656</v>
+        <v>0.6834093758975713</v>
       </c>
       <c r="BR113" t="n">
-        <v>0.5088351107178419</v>
+        <v>0.4109754847618769</v>
       </c>
       <c r="BS113" t="n">
-        <v>0.7898123804672214</v>
+        <v>0.6755328197010931</v>
       </c>
       <c r="BT113" t="n">
-        <v>0.8315445509746356</v>
+        <v>0.6950946188605088</v>
       </c>
       <c r="BU113" t="n">
-        <v>0.7931403667395385</v>
+        <v>0.6684206556975836</v>
       </c>
       <c r="BV113" t="n">
-        <v>0.8251072643794083</v>
+        <v>0.6994221939204885</v>
       </c>
       <c r="BW113" t="n">
-        <v>0.8116628893367726</v>
+        <v>0.7991451356532193</v>
       </c>
       <c r="BX113" t="n">
-        <v>0.7329042758537887</v>
+        <v>0.6566865408942568</v>
       </c>
       <c r="BY113" t="n">
-        <v>0.9652655414035184</v>
+        <v>0.9673582231390903</v>
       </c>
       <c r="BZ113" t="n">
-        <v>0.8032914837368291</v>
+        <v>0.6652604098839565</v>
       </c>
       <c r="CA113" t="n">
-        <v>0.8598881101264727</v>
+        <v>0.73101070177215</v>
       </c>
       <c r="CB113" t="n">
-        <v>0.585382345706969</v>
+        <v>0.5053080590929984</v>
       </c>
       <c r="CC113" t="n">
-        <v>0.8088833954989182</v>
+        <v>0.6884774097542743</v>
       </c>
       <c r="CD113" t="n">
-        <v>0.7086022605558421</v>
+        <v>0.6067192176329703</v>
       </c>
       <c r="CE113" t="n">
-        <v>0.7780572187107833</v>
+        <v>0.7318495315684566</v>
       </c>
       <c r="CF113" t="n">
-        <v>0.7716909650360607</v>
+        <v>0.6599698079290985</v>
       </c>
       <c r="CG113" t="n">
-        <v>0.5833454272438099</v>
+        <v>0.4424710809958134</v>
       </c>
       <c r="CH113" t="n">
-        <v>0.8190211637217893</v>
+        <v>0.7008211621578935</v>
       </c>
       <c r="CI113" t="n">
-        <v>0.8498200779465911</v>
+        <v>0.720378506991998</v>
       </c>
       <c r="CJ113" t="n">
-        <v>0.687346320715402</v>
+        <v>0.5696844781410231</v>
       </c>
       <c r="CK113" t="n">
-        <v>0.7697394235142676</v>
+        <v>0.6543892499367459</v>
       </c>
       <c r="CL113" t="n">
-        <v>0.8375639796283092</v>
+        <v>0.7136863225527214</v>
       </c>
       <c r="CM113" t="n">
-        <v>0.8400418919522978</v>
+        <v>0.7085254019681272</v>
       </c>
       <c r="CN113" t="n">
-        <v>0.9004575693443317</v>
+        <v>0.9065692216750525</v>
       </c>
       <c r="CO113" t="n">
-        <v>0.7540059517295651</v>
+        <v>0.6362681640905185</v>
       </c>
       <c r="CP113" t="n">
-        <v>0.7436808235091117</v>
+        <v>0.620046817625555</v>
       </c>
       <c r="CQ113" t="n">
-        <v>0.762540808025799</v>
+        <v>0.6338552997101233</v>
       </c>
       <c r="CR113" t="n">
-        <v>0.667198035271151</v>
+        <v>0.5670650263122676</v>
       </c>
       <c r="CS113" t="n">
-        <v>0.8041373083026447</v>
+        <v>0.684704274407879</v>
       </c>
       <c r="CT113" t="n">
-        <v>0.9319399589103291</v>
+        <v>0.9270763232978396</v>
       </c>
       <c r="CU113" t="n">
-        <v>0.8050033577445868</v>
+        <v>0.6885622781664629</v>
       </c>
       <c r="CV113" t="n">
-        <v>0.6539044287891452</v>
+        <v>0.5595195099378153</v>
       </c>
       <c r="CW113" t="n">
-        <v>0.7504234867494997</v>
+        <v>0.75403475824413</v>
       </c>
       <c r="CX113" t="n">
-        <v>0.7582071258656267</v>
+        <v>0.6495742375023035</v>
       </c>
       <c r="CY113" t="n">
-        <v>0.4116145960958516</v>
+        <v>0.3752009176891131</v>
       </c>
       <c r="CZ113" t="n">
-        <v>0.6168837304729783</v>
+        <v>0.581274832744944</v>
       </c>
       <c r="DA113" t="n">
-        <v>0.4591156383799239</v>
+        <v>0.2892736032130635</v>
       </c>
       <c r="DB113" t="n">
-        <v>0.4261445918378359</v>
+        <v>0.3807397818189809</v>
       </c>
       <c r="DC113" t="n">
-        <v>0.770540349481692</v>
+        <v>0.8141721274604552</v>
       </c>
       <c r="DD113" t="n">
-        <v>0.428173939367775</v>
+        <v>0.311266034154866</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.4982034065699665</v>
+        <v>0.3112887544084253</v>
       </c>
       <c r="DF113" t="n">
-        <v>0.663406058896421</v>
+        <v>0.5751292386936779</v>
       </c>
       <c r="DG113" t="n">
-        <v>0.6081754266667971</v>
+        <v>0.5312957695567525</v>
       </c>
       <c r="DH113" t="n">
-        <v>0.7578813145998073</v>
+        <v>0.650076042564238</v>
       </c>
       <c r="DI113" t="n">
         <v>0</v>
       </c>
       <c r="DJ113" t="n">
-        <v>0.6754765795447518</v>
+        <v>0.5879290473138531</v>
       </c>
     </row>
     <row r="114">
@@ -39759,340 +39759,340 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.564058747732799</v>
+        <v>0.5905151222264058</v>
       </c>
       <c r="C114" t="n">
-        <v>0.9040777537289109</v>
+        <v>0.926555888234502</v>
       </c>
       <c r="D114" t="n">
-        <v>0.680204066728038</v>
+        <v>0.7233781923675132</v>
       </c>
       <c r="E114" t="n">
-        <v>0.6370768914184206</v>
+        <v>0.6547923607682997</v>
       </c>
       <c r="F114" t="n">
-        <v>0.4368289056824829</v>
+        <v>0.4751240987034192</v>
       </c>
       <c r="G114" t="n">
-        <v>0.6335075760677472</v>
+        <v>0.6533221289353753</v>
       </c>
       <c r="H114" t="n">
-        <v>0.3881858254524245</v>
+        <v>0.4691311286591971</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5261934131398841</v>
+        <v>0.5546572487259466</v>
       </c>
       <c r="J114" t="n">
-        <v>0.2237960570356418</v>
+        <v>0.1455691952602586</v>
       </c>
       <c r="K114" t="n">
-        <v>0.2383760068130767</v>
+        <v>0.2985445069254152</v>
       </c>
       <c r="L114" t="n">
-        <v>0.2555563553357998</v>
+        <v>0.1008652528364949</v>
       </c>
       <c r="M114" t="n">
-        <v>0.5452722820842487</v>
+        <v>0.6087085679272927</v>
       </c>
       <c r="N114" t="n">
-        <v>0.8582181626984178</v>
+        <v>0.8827853033521215</v>
       </c>
       <c r="O114" t="n">
-        <v>0.8284911454513667</v>
+        <v>0.827710021973958</v>
       </c>
       <c r="P114" t="n">
-        <v>0.8760221246783719</v>
+        <v>0.8643313032473021</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.355772345172752</v>
+        <v>0.4086222026909004</v>
       </c>
       <c r="R114" t="n">
-        <v>0.2129670815997454</v>
+        <v>0.3139155682909374</v>
       </c>
       <c r="S114" t="n">
-        <v>0.748652555242988</v>
+        <v>0.7592124726805903</v>
       </c>
       <c r="T114" t="n">
-        <v>0.2419884893811775</v>
+        <v>0.07810538939197756</v>
       </c>
       <c r="U114" t="n">
-        <v>0.2979024161386215</v>
+        <v>0.1375859546086068</v>
       </c>
       <c r="V114" t="n">
-        <v>0.3225236382064094</v>
+        <v>0.1690998571180982</v>
       </c>
       <c r="W114" t="n">
-        <v>0.2433513179787903</v>
+        <v>0.3385393957575134</v>
       </c>
       <c r="X114" t="n">
-        <v>0.6060108249272838</v>
+        <v>0.6371260760420749</v>
       </c>
       <c r="Y114" t="n">
-        <v>0.2962035673585701</v>
+        <v>0.3574433642780199</v>
       </c>
       <c r="Z114" t="n">
-        <v>0.7915817495181655</v>
+        <v>0.782667076735775</v>
       </c>
       <c r="AA114" t="n">
-        <v>0.5588376175215569</v>
+        <v>0.6139514836696012</v>
       </c>
       <c r="AB114" t="n">
-        <v>0.5406232053469017</v>
+        <v>0.5676594864867252</v>
       </c>
       <c r="AC114" t="n">
-        <v>0.780584574704256</v>
+        <v>0.7972688119002851</v>
       </c>
       <c r="AD114" t="n">
-        <v>0.8025683739181378</v>
+        <v>0.8156267045248633</v>
       </c>
       <c r="AE114" t="n">
-        <v>0.3428191872739644</v>
+        <v>0.3974934268562424</v>
       </c>
       <c r="AF114" t="n">
-        <v>0.2272723912285929</v>
+        <v>0.314762038641579</v>
       </c>
       <c r="AG114" t="n">
-        <v>0.5489521561849215</v>
+        <v>0.5810590199750186</v>
       </c>
       <c r="AH114" t="n">
-        <v>0.8585399825559648</v>
+        <v>0.8792836659605621</v>
       </c>
       <c r="AI114" t="n">
-        <v>0.2299957505159447</v>
+        <v>0.2472172664004959</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0.2432368215259753</v>
+        <v>0.09388751159653928</v>
       </c>
       <c r="AK114" t="n">
-        <v>0.2635490147638415</v>
+        <v>0.1101912844320542</v>
       </c>
       <c r="AL114" t="n">
-        <v>0.6953437930210906</v>
+        <v>0.7169924973213386</v>
       </c>
       <c r="AM114" t="n">
-        <v>0.3901845400801141</v>
+        <v>0.4488765552923529</v>
       </c>
       <c r="AN114" t="n">
-        <v>0.609436769180295</v>
+        <v>0.6388818373951262</v>
       </c>
       <c r="AO114" t="n">
-        <v>0.3623793574319543</v>
+        <v>0.4202794643481624</v>
       </c>
       <c r="AP114" t="n">
-        <v>0.5226211977612119</v>
+        <v>0.5691883729648198</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.6301697284306647</v>
+        <v>0.655899597427451</v>
       </c>
       <c r="AR114" t="n">
-        <v>0.3347761707638779</v>
+        <v>0.3858735944699245</v>
       </c>
       <c r="AS114" t="n">
-        <v>0.5900871531932576</v>
+        <v>0.6547708122217322</v>
       </c>
       <c r="AT114" t="n">
-        <v>0.3324237608476598</v>
+        <v>0.1763868595859825</v>
       </c>
       <c r="AU114" t="n">
-        <v>0.2230010567956715</v>
+        <v>0.07148792438914692</v>
       </c>
       <c r="AV114" t="n">
-        <v>0.7717839702836753</v>
+        <v>0.7660408458238296</v>
       </c>
       <c r="AW114" t="n">
-        <v>0.8669926545774052</v>
+        <v>0.847456764659791</v>
       </c>
       <c r="AX114" t="n">
-        <v>0.5283348701431939</v>
+        <v>0.5996554165968405</v>
       </c>
       <c r="AY114" t="n">
-        <v>0.3986379954619315</v>
+        <v>0.4567209030995519</v>
       </c>
       <c r="AZ114" t="n">
-        <v>0.2917484562876466</v>
+        <v>0.1151123497820608</v>
       </c>
       <c r="BA114" t="n">
-        <v>0.7606495849740854</v>
+        <v>0.7762656066219911</v>
       </c>
       <c r="BB114" t="n">
-        <v>0.724042072936202</v>
+        <v>0.7246399974320996</v>
       </c>
       <c r="BC114" t="n">
-        <v>0.8489566844425108</v>
+        <v>0.8362634803321783</v>
       </c>
       <c r="BD114" t="n">
-        <v>0.5702729927087606</v>
+        <v>0.6049871536687653</v>
       </c>
       <c r="BE114" t="n">
-        <v>0.5092534881442331</v>
+        <v>0.5471246839752645</v>
       </c>
       <c r="BF114" t="n">
-        <v>0.2894878697484925</v>
+        <v>0.3663840999177265</v>
       </c>
       <c r="BG114" t="n">
-        <v>0.2215945910956589</v>
+        <v>0.2014149954836934</v>
       </c>
       <c r="BH114" t="n">
-        <v>0.2805383693729336</v>
+        <v>0.2804580173085978</v>
       </c>
       <c r="BI114" t="n">
-        <v>0.2213661335221531</v>
+        <v>0.1834540552283858</v>
       </c>
       <c r="BJ114" t="n">
-        <v>0.2612496943768693</v>
+        <v>0.08398948473771711</v>
       </c>
       <c r="BK114" t="n">
-        <v>0.3021884128311983</v>
+        <v>0.1202261868653769</v>
       </c>
       <c r="BL114" t="n">
-        <v>0.5579433464134559</v>
+        <v>0.5978801784807587</v>
       </c>
       <c r="BM114" t="n">
-        <v>0.370076992216375</v>
+        <v>0.4327970366995269</v>
       </c>
       <c r="BN114" t="n">
-        <v>0.3158090893657367</v>
+        <v>0.1311082218150844</v>
       </c>
       <c r="BO114" t="n">
-        <v>0.2853159552454234</v>
+        <v>0.179682823510148</v>
       </c>
       <c r="BP114" t="n">
-        <v>0.3079446720700444</v>
+        <v>0.1241077279809608</v>
       </c>
       <c r="BQ114" t="n">
-        <v>0.2802712482972228</v>
+        <v>0.1327984872550846</v>
       </c>
       <c r="BR114" t="n">
-        <v>0.7289158849496207</v>
+        <v>0.738791350641931</v>
       </c>
       <c r="BS114" t="n">
-        <v>0.2943386975691636</v>
+        <v>0.1294762348709801</v>
       </c>
       <c r="BT114" t="n">
-        <v>0.2895295038316317</v>
+        <v>0.140049324420084</v>
       </c>
       <c r="BU114" t="n">
-        <v>0.2704011611053865</v>
+        <v>0.1173864727774023</v>
       </c>
       <c r="BV114" t="n">
-        <v>0.3106273415347734</v>
+        <v>0.1552936237520109</v>
       </c>
       <c r="BW114" t="n">
-        <v>0.7596671919020944</v>
+        <v>0.7919154817473382</v>
       </c>
       <c r="BX114" t="n">
-        <v>0.6211163901613654</v>
+        <v>0.6458352615352541</v>
       </c>
       <c r="BY114" t="n">
-        <v>0.9391918444002871</v>
+        <v>0.956287740349565</v>
       </c>
       <c r="BZ114" t="n">
-        <v>0.2623635727548937</v>
+        <v>0.3395510221412917</v>
       </c>
       <c r="CA114" t="n">
-        <v>0.3380839359685767</v>
+        <v>0.1813411266370316</v>
       </c>
       <c r="CB114" t="n">
-        <v>0.1950144753949476</v>
+        <v>0.2145261427720901</v>
       </c>
       <c r="CC114" t="n">
-        <v>0.2669502816161595</v>
+        <v>0.1105349588999806</v>
       </c>
       <c r="CD114" t="n">
-        <v>0.1991424096247628</v>
+        <v>0.1588376376044736</v>
       </c>
       <c r="CE114" t="n">
-        <v>0.6807214846340734</v>
+        <v>0.7309591052253744</v>
       </c>
       <c r="CF114" t="n">
-        <v>0.2596304905186314</v>
+        <v>0.08170919421646668</v>
       </c>
       <c r="CG114" t="n">
-        <v>0.5025519646264477</v>
+        <v>0.5545083931542631</v>
       </c>
       <c r="CH114" t="n">
-        <v>0.2870407806442672</v>
+        <v>0.2047714235043131</v>
       </c>
       <c r="CI114" t="n">
-        <v>0.3015373826382874</v>
+        <v>0.1558540693708217</v>
       </c>
       <c r="CJ114" t="n">
-        <v>0.2920741616348765</v>
+        <v>0.3916611858176881</v>
       </c>
       <c r="CK114" t="n">
-        <v>0.2749633928515838</v>
+        <v>0.0891362378125284</v>
       </c>
       <c r="CL114" t="n">
-        <v>0.3079892723302376</v>
+        <v>0.1558984209107271</v>
       </c>
       <c r="CM114" t="n">
-        <v>0.2903690944826552</v>
+        <v>0.1355036433449252</v>
       </c>
       <c r="CN114" t="n">
-        <v>0.8853057553059356</v>
+        <v>0.8995712722373003</v>
       </c>
       <c r="CO114" t="n">
-        <v>0.2045782828331663</v>
+        <v>0.09188356916539568</v>
       </c>
       <c r="CP114" t="n">
-        <v>0.273912995986782</v>
+        <v>0.3388353588200513</v>
       </c>
       <c r="CQ114" t="n">
-        <v>0.2586912322008871</v>
+        <v>0.08391688406131999</v>
       </c>
       <c r="CR114" t="n">
-        <v>0.4998440089510464</v>
+        <v>0.5385823973663532</v>
       </c>
       <c r="CS114" t="n">
-        <v>0.2728268179141453</v>
+        <v>0.1138671600000108</v>
       </c>
       <c r="CT114" t="n">
-        <v>0.9113078247071006</v>
+        <v>0.9317456820826514</v>
       </c>
       <c r="CU114" t="n">
-        <v>0.2685262337429998</v>
+        <v>0.1109058878210318</v>
       </c>
       <c r="CV114" t="n">
-        <v>0.4997037282865862</v>
+        <v>0.5447803893840825</v>
       </c>
       <c r="CW114" t="n">
-        <v>0.7472607827516454</v>
+        <v>0.7480113381847038</v>
       </c>
       <c r="CX114" t="n">
-        <v>0.2480529142280245</v>
+        <v>0.1152083335316573</v>
       </c>
       <c r="CY114" t="n">
-        <v>0.2332598144624723</v>
+        <v>0.2296201236888218</v>
       </c>
       <c r="CZ114" t="n">
-        <v>0.9371952881682651</v>
+        <v>0.9121686735877003</v>
       </c>
       <c r="DA114" t="n">
-        <v>0.5885212545047881</v>
+        <v>0.6081611008680131</v>
       </c>
       <c r="DB114" t="n">
-        <v>0.2324369386328306</v>
+        <v>0.2782952314959878</v>
       </c>
       <c r="DC114" t="n">
-        <v>0.8025572253574282</v>
+        <v>0.7929602171344868</v>
       </c>
       <c r="DD114" t="n">
-        <v>0.235770039159101</v>
+        <v>0.3080809599771341</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.3154270296153226</v>
+        <v>0.3735761676448657</v>
       </c>
       <c r="DF114" t="n">
-        <v>0.2222914789436459</v>
+        <v>0.1344216727812139</v>
       </c>
       <c r="DG114" t="n">
-        <v>0.3012022588271058</v>
+        <v>0.1366887526674703</v>
       </c>
       <c r="DH114" t="n">
-        <v>0.2619232671545096</v>
+        <v>0.1004064674291194</v>
       </c>
       <c r="DI114" t="n">
-        <v>0.6754765795447518</v>
+        <v>0.5879290473138531</v>
       </c>
       <c r="DJ114" t="n">
         <v>0</v>
